--- a/Exp3_PTO_GRPO/eda/results/arms/validity/tables/claude-haiku-4-5/validity.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/validity/tables/claude-haiku-4-5/validity.xlsx
@@ -503,40 +503,40 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>52.4</v>
+        <v>52</v>
       </c>
       <c r="D2" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="F2" t="n">
-        <v>0.418</v>
+        <v>0.42</v>
       </c>
       <c r="G2" t="n">
-        <v>0.414</v>
+        <v>0.415</v>
       </c>
       <c r="H2" t="n">
-        <v>0.42</v>
+        <v>0.421</v>
       </c>
       <c r="I2" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="J2" t="n">
-        <v>0.407</v>
+        <v>0.4</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.082</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.03</v>
+        <v>-0.031</v>
       </c>
       <c r="M2" t="n">
         <v>0.165</v>
       </c>
       <c r="N2" t="n">
-        <v>0.074</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="3">
@@ -549,40 +549,40 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>51.4</v>
+        <v>50.8</v>
       </c>
       <c r="D3" t="n">
         <v>13.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.385</v>
+        <v>0.386</v>
       </c>
       <c r="F3" t="n">
-        <v>0.422</v>
+        <v>0.423</v>
       </c>
       <c r="G3" t="n">
-        <v>0.418</v>
+        <v>0.42</v>
       </c>
       <c r="H3" t="n">
-        <v>0.425</v>
+        <v>0.427</v>
       </c>
       <c r="I3" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="J3" t="n">
-        <v>0.405</v>
+        <v>0.396</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.017</v>
+        <v>-0.019</v>
       </c>
       <c r="L3" t="n">
         <v>-0.095</v>
       </c>
       <c r="M3" t="n">
-        <v>0.142</v>
+        <v>0.143</v>
       </c>
       <c r="N3" t="n">
-        <v>0.033</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="4">
@@ -595,40 +595,40 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>53.4</v>
+        <v>53.1</v>
       </c>
       <c r="D4" t="n">
         <v>16.3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="F4" t="n">
-        <v>0.414</v>
+        <v>0.415</v>
       </c>
       <c r="G4" t="n">
         <v>0.41</v>
       </c>
       <c r="H4" t="n">
-        <v>0.414</v>
+        <v>0.415</v>
       </c>
       <c r="I4" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="J4" t="n">
-        <v>0.405</v>
+        <v>0.399</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.105</v>
+        <v>-0.107</v>
       </c>
       <c r="L4" t="n">
         <v>0.051</v>
       </c>
       <c r="M4" t="n">
-        <v>0.165</v>
+        <v>0.166</v>
       </c>
       <c r="N4" t="n">
-        <v>0.129</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="5">
@@ -641,40 +641,40 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>53.1</v>
+        <v>52.6</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="F5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.418</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.417</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="J5" t="n">
-        <v>0.406</v>
+        <v>0.398</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.057</v>
+        <v>-0.06</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.079</v>
+        <v>-0.082</v>
       </c>
       <c r="M5" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="N5" t="n">
-        <v>0.066</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -687,37 +687,37 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>53.9</v>
+        <v>53.6</v>
       </c>
       <c r="D6" t="n">
         <v>16.7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="F6" t="n">
-        <v>0.413</v>
+        <v>0.414</v>
       </c>
       <c r="G6" t="n">
-        <v>0.407</v>
+        <v>0.406</v>
       </c>
       <c r="H6" t="n">
-        <v>0.415</v>
+        <v>0.416</v>
       </c>
       <c r="I6" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="J6" t="n">
-        <v>0.405</v>
+        <v>0.401</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.166</v>
+        <v>-0.168</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="M6" t="n">
-        <v>0.133</v>
+        <v>0.132</v>
       </c>
       <c r="N6" t="n">
         <v>0.131</v>
